--- a/data/trending_integrated_20260908_10.xlsx
+++ b/data/trending_integrated_20260908_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>139756897823</v>
+        <v>140455533943</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 국책사업 선정 및 6G 광통신 부품 사업 본격화. 정부 주도 국산화 이슈 부각.</t>
+          <t>AI 데이터센터, 6G 광통신 관련 정부 주관 사업 선정 뉴스가 부각되며 급등. AI 바람 재차 불면 추가 상승 기대감 높음.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI데이터센터', '국책사업', '광통신']</t>
+          <t>['AI', '광통신', '정부 사업']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10760</v>
+        <v>10640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+27.79%</t>
+          <t>+26.37%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -693,7 +693,7 @@
         <v>8640</v>
       </c>
       <c r="L3" t="n">
-        <v>10900</v>
+        <v>10940</v>
       </c>
       <c r="M3" t="n">
         <v>8230</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>172137579505</v>
+        <v>239541510935</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부 정책 기대감 속 미프진 독점 판매 이슈 부각. 기대감에 따른 급등 전망.</t>
+          <t>정부의 저출산 대책으로 미프진 관련주로 부각되며 상승 기대감 형성. 그러나 구체적인 공시나 뉴스는 부족.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '정부정책', '독점판매']</t>
+          <t>['미프진', '정부 정책']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36850</v>
+        <v>36900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.62%</t>
+          <t>+20.79%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="F4" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="G4" t="n">
-        <v>606</v>
+        <v>738</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>650516473450</v>
+        <v>683388640725</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 지분 공시 및 주포 활동 언급. 비교군 없는 신규 상장주로 분석.</t>
+          <t>정부 지분 공시, 비교군 없는 신규 상장주로서의 기대감 및 급등 조짐.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['지분공시', '주포', '신규주']</t>
+          <t>['신규주', '정부 지분', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4100</v>
+        <v>4160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+14.53%</t>
+          <t>+16.20%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="H5" t="n">
         <v>1.56</v>
@@ -877,7 +877,7 @@
         <v>3600</v>
       </c>
       <c r="L5" t="n">
-        <v>4200</v>
+        <v>4335</v>
       </c>
       <c r="M5" t="n">
         <v>3450</v>
@@ -886,10 +886,10 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>117566955541</v>
+        <v>192711605976</v>
       </c>
       <c r="P5" t="n">
-        <v>4200</v>
+        <v>4335</v>
       </c>
       <c r="Q5" t="n">
         <v>1246</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>탈모 관련 건보 적용 기대감 및 현대약품과의 동반 상승 가능성. 매력적인 가격 구간 진입.</t>
+          <t>탈모 건보료 적용 시 난리 날 것이라는 기대감과 함께 10년 매집 구간 돌파 및 30만 목표가 제시. 약효에 대한 긍정적 평가.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['탈모', '건보적용', '현대약품']</t>
+          <t>['탈모', '건보료', '신약']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,79 +931,79 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>337</v>
+        <v>137700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+12.71%</t>
+          <t>+12.59%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="E6" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="H6" t="n">
-        <v>5.34</v>
+        <v>13.33</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>299</v>
+        <v>122300</v>
       </c>
       <c r="K6" t="n">
-        <v>220</v>
+        <v>129400</v>
       </c>
       <c r="L6" t="n">
-        <v>349</v>
+        <v>143100</v>
       </c>
       <c r="M6" t="n">
-        <v>220</v>
+        <v>128100</v>
       </c>
       <c r="N6" t="n">
-        <v>5.29</v>
+        <v>13.22</v>
       </c>
       <c r="O6" t="n">
-        <v>6256043195</v>
+        <v>136963977850</v>
       </c>
       <c r="P6" t="n">
-        <v>901</v>
+        <v>198000</v>
       </c>
       <c r="Q6" t="n">
-        <v>217</v>
+        <v>77100</v>
       </c>
       <c r="R6" t="n">
-        <v>645000</v>
+        <v>-37000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>51000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>상장폐지 관련 공시 확인 및 정리매매 가능성. 회사 자산 대비 시총이 크다는 분석.</t>
+          <t>미국 원전 8기 수주 관련 대형 사업 언급, AP1000 사업 및 웨스팅 지분 급물살.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['상장폐지', '정리매매', '자산']</t>
+          <t>['원전', 'AP1000', '미국 수주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>052690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>136300</v>
+        <v>20450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+11.45%</t>
+          <t>+11.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
-        <v>130</v>
+        <v>498</v>
       </c>
       <c r="H7" t="n">
-        <v>13.33</v>
+        <v>10.47</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>122300</v>
+        <v>18410</v>
       </c>
       <c r="K7" t="n">
-        <v>129400</v>
+        <v>18800</v>
       </c>
       <c r="L7" t="n">
-        <v>143100</v>
+        <v>20725</v>
       </c>
       <c r="M7" t="n">
-        <v>128100</v>
+        <v>18480</v>
       </c>
       <c r="N7" t="n">
-        <v>13.22</v>
+        <v>10.4</v>
       </c>
       <c r="O7" t="n">
-        <v>132312047350</v>
+        <v>274267825940</v>
       </c>
       <c r="P7" t="n">
-        <v>198000</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>77100</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-37000</v>
+        <v>-8000</v>
       </c>
       <c r="S7" t="n">
-        <v>51000</v>
+        <v>85000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 대형 사업 관련 뉴스 및 웨스팅하우스 지분 급물살. 260조 사업 규모와 수익 계산 포함.</t>
+          <t>원전 사업 복 터졌다는 기대감과 함께 2만 원 돌파 및 신사업 재료 발표 기대감 상승. 다만, 확정된 내용은 아직 없음.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '웨스팅하우스', '사업규모']</t>
+          <t>['원전', '신사업', '건설']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20150</v>
+        <v>331</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.45%</t>
+          <t>+10.70%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="F8" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>337</v>
+        <v>38</v>
       </c>
       <c r="H8" t="n">
-        <v>10.47</v>
+        <v>5.34</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18410</v>
+        <v>299</v>
       </c>
       <c r="K8" t="n">
-        <v>18800</v>
+        <v>220</v>
       </c>
       <c r="L8" t="n">
-        <v>20300</v>
+        <v>349</v>
       </c>
       <c r="M8" t="n">
-        <v>18480</v>
+        <v>220</v>
       </c>
       <c r="N8" t="n">
-        <v>10.4</v>
+        <v>5.29</v>
       </c>
       <c r="O8" t="n">
-        <v>223235878415</v>
+        <v>6781829232</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>901</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>217</v>
       </c>
       <c r="R8" t="n">
-        <v>-8000</v>
+        <v>645000</v>
       </c>
       <c r="S8" t="n">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원전 사업 부각 및 신사업 재료 발표 기대감. 상반기 순이익 급증으로 인한 긍정적 전망.</t>
+          <t>상장폐지 가능성 속 정리매매 진행, 상속 지분 및 자산 가치 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '신사업', '순이익']</t>
+          <t>['상장폐지', '정리매매', '자산 가치']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11750</v>
+        <v>11700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.60%</t>
+          <t>+7.14%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.11</v>
       </c>
       <c r="E9" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G9" t="n">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="H9" t="n">
         <v>5.42</v>
@@ -1254,7 +1254,7 @@
         <v>5.53</v>
       </c>
       <c r="O9" t="n">
-        <v>91446062600</v>
+        <v>95919571905</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원전 섹터 관련 협정 및 공매도 이슈 언급. 거래량 대비 높은 가격 상승 기대.</t>
+          <t>원전 섹터 관련 협정 및 투자 소식, 공매도 상환 압박 및 2조 시총 논란.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '협정']</t>
+          <t>['원전', '공매도', '프랑스 협정']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14120</v>
+        <v>50400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.83%</t>
+          <t>+5.00%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>327</v>
+        <v>168</v>
       </c>
       <c r="H10" t="n">
-        <v>1.94</v>
+        <v>38.34</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13470</v>
+        <v>48000</v>
       </c>
       <c r="K10" t="n">
-        <v>13580</v>
+        <v>48550</v>
       </c>
       <c r="L10" t="n">
-        <v>14450</v>
+        <v>51600</v>
       </c>
       <c r="M10" t="n">
-        <v>13420</v>
+        <v>48350</v>
       </c>
       <c r="N10" t="n">
-        <v>1.82</v>
+        <v>38.24</v>
       </c>
       <c r="O10" t="n">
-        <v>163124443610</v>
+        <v>92505033275</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>67300</v>
       </c>
       <c r="Q10" t="n">
-        <v>1252</v>
+        <v>23150</v>
       </c>
       <c r="R10" t="n">
-        <v>20000</v>
+        <v>266000</v>
       </c>
       <c r="S10" t="n">
-        <v>5000</v>
+        <v>40000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Texas 관련 소식 및 공매도 언급. 투경재 지정 판단일 관련 내용 포함.</t>
+          <t>건설주 전반의 상승세와 함께 원전, 재건 등 다양한 테마 기대감 존재. 그러나 단기 급등 후 조정 가능성 및 개인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['Texas', '공매도', '투경재']</t>
+          <t>['건설', '원전', '재건']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50200</v>
+        <v>14100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>+4.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>144</v>
+        <v>369</v>
       </c>
       <c r="H11" t="n">
-        <v>38.34</v>
+        <v>1.94</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>48000</v>
+        <v>13470</v>
       </c>
       <c r="K11" t="n">
-        <v>48550</v>
+        <v>13580</v>
       </c>
       <c r="L11" t="n">
-        <v>51600</v>
+        <v>14450</v>
       </c>
       <c r="M11" t="n">
-        <v>48350</v>
+        <v>13420</v>
       </c>
       <c r="N11" t="n">
-        <v>38.24</v>
+        <v>1.82</v>
       </c>
       <c r="O11" t="n">
-        <v>85981058225</v>
+        <v>171748424080</v>
       </c>
       <c r="P11" t="n">
-        <v>67300</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>23150</v>
+        <v>1252</v>
       </c>
       <c r="R11" t="n">
-        <v>266000</v>
+        <v>20000</v>
       </c>
       <c r="S11" t="n">
-        <v>40000</v>
+        <v>5000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>건설, 원전, 재건 등 복합 테마 기대감. 5만원대 안착 시 추가 상승 전망.</t>
+          <t>Texas 소식과 함께 큰 폭 상승 기대, 공매도 물량 언급 및 매물대 소화 과정.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['건설', '원전', '재건']</t>
+          <t>['광통신', '공매도', '매물대']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>91200</v>
+        <v>9180</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.75%</t>
+          <t>+4.56%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>326</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
-        <v>213</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>1612</v>
+        <v>33</v>
       </c>
       <c r="H12" t="n">
-        <v>23.63</v>
+        <v>1.68</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>87900</v>
+        <v>8780</v>
       </c>
       <c r="K12" t="n">
-        <v>91200</v>
+        <v>9060</v>
       </c>
       <c r="L12" t="n">
-        <v>93500</v>
+        <v>9960</v>
       </c>
       <c r="M12" t="n">
-        <v>90200</v>
+        <v>8270</v>
       </c>
       <c r="N12" t="n">
-        <v>23.53</v>
+        <v>1.72</v>
       </c>
       <c r="O12" t="n">
-        <v>264688603100</v>
+        <v>90007819410</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>25050</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>3705</v>
       </c>
       <c r="R12" t="n">
-        <v>-211000</v>
+        <v>51000</v>
       </c>
       <c r="S12" t="n">
-        <v>236000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
+          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '텍사스']</t>
+          <t>['투경', '탈모 테마', 'JAK 억제']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33800</v>
+        <v>91600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.21%</t>
+          <t>+4.21%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>57</v>
+        <v>345</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>221</v>
       </c>
       <c r="G13" t="n">
-        <v>189</v>
+        <v>1669</v>
       </c>
       <c r="H13" t="n">
-        <v>52.67</v>
+        <v>23.63</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>32750</v>
+        <v>87900</v>
       </c>
       <c r="K13" t="n">
-        <v>33700</v>
+        <v>91200</v>
       </c>
       <c r="L13" t="n">
-        <v>34350</v>
+        <v>93500</v>
       </c>
       <c r="M13" t="n">
-        <v>33450</v>
+        <v>90200</v>
       </c>
       <c r="N13" t="n">
-        <v>21.02</v>
+        <v>23.53</v>
       </c>
       <c r="O13" t="n">
-        <v>44485162425</v>
+        <v>280149092250</v>
       </c>
       <c r="P13" t="n">
-        <v>69500</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>30400</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>290000</v>
+        <v>-211000</v>
       </c>
       <c r="S13" t="n">
-        <v>157000</v>
+        <v>236000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 및 미국 원전 사업 추진 본격화. 공매도 물량 소화 후 상승 기대.</t>
+          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '원전', '공매도']</t>
+          <t>['원전', 'SMR', '텍사스']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1837000</v>
+        <v>1850000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+3.76%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F14" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G14" t="n">
-        <v>1837</v>
+        <v>2039</v>
       </c>
       <c r="H14" t="n">
         <v>50.63</v>
@@ -1714,7 +1714,7 @@
         <v>50.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2336835759500</v>
+        <v>2606620111500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>기관 및 외인 매수세 유입에 따른 반도체 업황 개선 기대. 치명적인 저평가 구간 진입.</t>
+          <t>낸드 메모리 품귀 현상 및 반도체 시즌2 도래 전망. 기관·외인 재매수세 유입되며 300만 돌파 기대감 고조. 자사주 매수 및 숏 악귀 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '기관외인', '저평가']</t>
+          <t>['낸드 메모리', '반도체', '자사주 매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>273500</v>
+        <v>33850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>798</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
-        <v>474</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>1751</v>
+        <v>220</v>
       </c>
       <c r="H15" t="n">
-        <v>46.79</v>
+        <v>52.67</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>270000</v>
+        <v>32750</v>
       </c>
       <c r="K15" t="n">
-        <v>272000</v>
+        <v>33700</v>
       </c>
       <c r="L15" t="n">
-        <v>275000</v>
+        <v>34350</v>
       </c>
       <c r="M15" t="n">
-        <v>269000</v>
+        <v>33450</v>
       </c>
       <c r="N15" t="n">
-        <v>46.73</v>
+        <v>21.02</v>
       </c>
       <c r="O15" t="n">
-        <v>1388196998500</v>
+        <v>48111481200</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>69500</v>
       </c>
       <c r="Q15" t="n">
-        <v>69600</v>
+        <v>30400</v>
       </c>
       <c r="R15" t="n">
-        <v>498000</v>
+        <v>290000</v>
       </c>
       <c r="S15" t="n">
-        <v>160000</v>
+        <v>157000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>자사주 매수 및 주주환원 정책 기대감. 단기적 공매도 및 개인 매물 출회.</t>
+          <t>미국 웨스팅하우스 지분 인수 및 원전 사업 관련 호재. PBR 저평가 및 공매도 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주매수', '주주환원', '공매도']</t>
+          <t>['웨스팅하우스', '원전', 'PBR']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10060</v>
+        <v>15050</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H16" t="n">
-        <v>0.44</v>
+        <v>1.72</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,47 +1883,47 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>10200</v>
+        <v>14650</v>
       </c>
       <c r="K16" t="n">
-        <v>10600</v>
+        <v>15100</v>
       </c>
       <c r="L16" t="n">
-        <v>10970</v>
+        <v>16680</v>
       </c>
       <c r="M16" t="n">
-        <v>9980</v>
+        <v>14800</v>
       </c>
       <c r="N16" t="n">
-        <v>0.21</v>
+        <v>1.58</v>
       </c>
       <c r="O16" t="n">
-        <v>51064233465</v>
+        <v>42075117990</v>
       </c>
       <c r="P16" t="n">
-        <v>20850</v>
+        <v>21400</v>
       </c>
       <c r="Q16" t="n">
-        <v>4020</v>
+        <v>12090</v>
       </c>
       <c r="R16" t="n">
-        <v>-7000</v>
+        <v>35000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>터빈 블레이드 수주 기대감 및 뉴스 언급. 미국 가스터빈 독점 공급 관련 분석.</t>
+          <t>스카이랩스 대비 저평가 언급, 단타 및 자전거래 의혹, 보호예수 물량 주의.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['가스터빈', '수주', '독점공급']</t>
+          <t>['단타', '자전거래', '보호예수']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>0155E0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15560</v>
+        <v>276000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.41%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>62</v>
+        <v>799</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>464</v>
       </c>
       <c r="G17" t="n">
-        <v>243</v>
+        <v>1723</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>46.79</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>16110</v>
+        <v>270000</v>
       </c>
       <c r="K17" t="n">
-        <v>16130</v>
+        <v>272000</v>
       </c>
       <c r="L17" t="n">
-        <v>16140</v>
+        <v>276000</v>
       </c>
       <c r="M17" t="n">
-        <v>15310</v>
+        <v>269000</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>46.73</v>
       </c>
       <c r="O17" t="n">
-        <v>26097154465</v>
+        <v>1719792942750</v>
       </c>
       <c r="P17" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q17" t="n">
-        <v>3200</v>
+        <v>69600</v>
       </c>
       <c r="R17" t="n">
-        <v>-57000</v>
+        <v>498000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>호남 메가 프로젝트 및 대규모 투자 유치 기대감. 광주 개발 등 연계 호재 부각.</t>
+          <t>자사주 15조 매수 뉴스가 부각되며 주가 상승 기대감 형성. 그러나 일부 투자자들의 매도 움직임과 정치적 언급도 혼재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['메가프로젝트', '대규모투자', '광주개발']</t>
+          <t>['자사주 매수', '반도체']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8410</v>
+        <v>10200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-11.10%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="H18" t="n">
-        <v>38.84</v>
+        <v>0.44</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>9460</v>
+        <v>10200</v>
       </c>
       <c r="K18" t="n">
-        <v>9700</v>
+        <v>10600</v>
       </c>
       <c r="L18" t="n">
-        <v>9760</v>
+        <v>10970</v>
       </c>
       <c r="M18" t="n">
-        <v>8110</v>
+        <v>9980</v>
       </c>
       <c r="N18" t="n">
-        <v>38.69</v>
+        <v>0.21</v>
       </c>
       <c r="O18" t="n">
-        <v>20333802075</v>
+        <v>54619762390</v>
       </c>
       <c r="P18" t="n">
-        <v>19150</v>
+        <v>20850</v>
       </c>
       <c r="Q18" t="n">
-        <v>3445</v>
+        <v>4020</v>
       </c>
       <c r="R18" t="n">
-        <v>53000</v>
+        <v>-7000</v>
       </c>
       <c r="S18" t="n">
-        <v>-14000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>삼성, 포스코 관계사 상승 언급 및 차익 실현 가능성. 대차잔고 및 프로그램 매수 관련 논의.</t>
+          <t>터빈블레이드 수주 기대감, 원전 및 헷지주 분류 논란, 변동성 속 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['관계사', '차익실현', '대차잔고']</t>
+          <t>['터빈블레이드', '수주', '가스터빈']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>340</v>
+        <v>15480</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-90.71%</t>
+          <t>-3.91%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3660</v>
+        <v>16110</v>
       </c>
       <c r="K19" t="n">
-        <v>300</v>
+        <v>16130</v>
       </c>
       <c r="L19" t="n">
-        <v>340</v>
+        <v>16140</v>
       </c>
       <c r="M19" t="n">
-        <v>300</v>
+        <v>15310</v>
       </c>
       <c r="N19" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>614195520</v>
+        <v>28039386470</v>
       </c>
       <c r="P19" t="n">
-        <v>3660</v>
+        <v>19380</v>
       </c>
       <c r="Q19" t="n">
-        <v>300</v>
+        <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>38000</v>
+        <v>-57000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>감사의견 적정 확보에도 불구하고 유증 물량 및 재무 악화 우려. 급락 후 회복 기대.</t>
+          <t>반도체 섹터 조정과 건설주 상승 흐름 속에서 금호건설은 뚜렷한 호재 없이 부진. 광주공항 재개 등 일부 테마 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,18 +2199,294 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['감사의견', '유증', '재무악화']</t>
+          <t>['건설', '광주공항']</t>
         </is>
       </c>
       <c r="X19" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>금호전기</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>12160</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-4.10%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>41</v>
+      </c>
+      <c r="F20" t="n">
+        <v>29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>105</v>
+      </c>
+      <c r="H20" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>12680</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12680</v>
+      </c>
+      <c r="L20" t="n">
+        <v>12680</v>
+      </c>
+      <c r="M20" t="n">
+        <v>11550</v>
+      </c>
+      <c r="N20" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="O20" t="n">
+        <v>21988104080</v>
+      </c>
+      <c r="P20" t="n">
+        <v>14350</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>465</v>
+      </c>
+      <c r="R20" t="n">
+        <v>9000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>계단식 하락 추세 지속되며 하한가 우려 제기. 반도체 섹터 조정과 외인 프로그램 매도세 속 투자 심리 위축.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['하락 추세', '반도체']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>001210</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>8430</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-10.89%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E21" t="n">
+        <v>52</v>
+      </c>
+      <c r="F21" t="n">
+        <v>32</v>
+      </c>
+      <c r="G21" t="n">
+        <v>116</v>
+      </c>
+      <c r="H21" t="n">
+        <v>38.84</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>9460</v>
+      </c>
+      <c r="K21" t="n">
+        <v>9700</v>
+      </c>
+      <c r="L21" t="n">
+        <v>9760</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8110</v>
+      </c>
+      <c r="N21" t="n">
+        <v>38.69</v>
+      </c>
+      <c r="O21" t="n">
+        <v>22510046425</v>
+      </c>
+      <c r="P21" t="n">
+        <v>19150</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3445</v>
+      </c>
+      <c r="R21" t="n">
+        <v>53000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-14000</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>삼성, 포스코 관계사 대비 부진, 매도 조장 및 대차잔고 관련 우려.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['포스코', '대차잔고', '매도 조장']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
         <v>1</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>033790</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>카프로</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>251</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-93.14%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>56</v>
+      </c>
+      <c r="F22" t="n">
+        <v>40</v>
+      </c>
+      <c r="G22" t="n">
+        <v>122</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>3660</v>
+      </c>
+      <c r="K22" t="n">
+        <v>300</v>
+      </c>
+      <c r="L22" t="n">
+        <v>340</v>
+      </c>
+      <c r="M22" t="n">
+        <v>251</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O22" t="n">
+        <v>668255900</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3660</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>251</v>
+      </c>
+      <c r="R22" t="n">
+        <v>38000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>감사의견 적정으로 거래 재개 기대감 있었으나, 유증 물량과 재무 상태에 대한 우려로 주가 급락. 향후 전망 불투명.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['감사의견', '유증']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>006380</t>
         </is>

--- a/data/trending_integrated_20260908_10.xlsx
+++ b/data/trending_integrated_20260908_10.xlsx
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F2" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>140455533943</v>
+        <v>140745973183</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터, 6G 광통신 관련 정부 주관 사업 선정 뉴스가 부각되며 급등. AI 바람 재차 불면 추가 상승 기대감 높음.</t>
+          <t>AI 데이터센터 국산화 수행기관 선정 및 6G 광통신 부품 사업 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '정부 사업']</t>
+          <t>['AI', '데이터센터', '광통신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10640</v>
+        <v>10520</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+26.37%</t>
+          <t>+24.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>239541510935</v>
+        <v>245312281155</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 저출산 대책으로 미프진 관련주로 부각되며 상승 기대감 형성. 그러나 구체적인 공시나 뉴스는 부족.</t>
+          <t>정부의 미프진 도입 추진 관련 기대감. 투자 유치 및 상한가 기록.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '정부 정책']</t>
+          <t>['미프진', '정부 정책', '상한가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36900</v>
+        <v>36750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.79%</t>
+          <t>+20.29%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="F4" t="n">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="G4" t="n">
-        <v>738</v>
+        <v>756</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>683388640725</v>
+        <v>689420350825</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 지분 공시, 비교군 없는 신규 상장주로서의 기대감 및 급등 조짐.</t>
+          <t>정부 지분 공시와 세계 최초 비침습 혈당 측정 기술에 대한 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['신규주', '정부 지분', '주포']</t>
+          <t>['혈당 측정', '정부 지분', '기술']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4160</v>
+        <v>4110</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.20%</t>
+          <t>+14.80%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="H5" t="n">
         <v>1.56</v>
@@ -886,7 +886,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>192711605976</v>
+        <v>206199635125</v>
       </c>
       <c r="P5" t="n">
         <v>4335</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>탈모 건보료 적용 시 난리 날 것이라는 기대감과 함께 10년 매집 구간 돌파 및 30만 목표가 제시. 약효에 대한 긍정적 평가.</t>
+          <t>탈모 치료제 관련 기대감. 건보 적용 시 큰 상승 예상. 10년 매집 구간.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['탈모', '건보료', '신약']</t>
+          <t>['탈모 치료제', '건보 적용', '신약']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>137700</v>
+        <v>138800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+12.59%</t>
+          <t>+13.49%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.11</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H6" t="n">
         <v>13.33</v>
@@ -978,7 +978,7 @@
         <v>13.22</v>
       </c>
       <c r="O6" t="n">
-        <v>136963977850</v>
+        <v>140466722250</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 원전 8기 수주 관련 대형 사업 언급, AP1000 사업 및 웨스팅 지분 급물살.</t>
+          <t>미국 원전 8기 수주 가능성과 신사업 진출 재료로 인한 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', 'AP1000', '미국 수주']</t>
+          <t>['원전', '신사업', 'AP1000']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20450</v>
+        <v>20750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+11.08%</t>
+          <t>+12.71%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="F7" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G7" t="n">
-        <v>498</v>
+        <v>559</v>
       </c>
       <c r="H7" t="n">
         <v>10.47</v>
@@ -1061,7 +1061,7 @@
         <v>18800</v>
       </c>
       <c r="L7" t="n">
-        <v>20725</v>
+        <v>20850</v>
       </c>
       <c r="M7" t="n">
         <v>18480</v>
@@ -1070,7 +1070,7 @@
         <v>10.4</v>
       </c>
       <c r="O7" t="n">
-        <v>274267825940</v>
+        <v>291884232215</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 사업 복 터졌다는 기대감과 함께 2만 원 돌파 및 신사업 재료 발표 기대감 상승. 다만, 확정된 내용은 아직 없음.</t>
+          <t>원전 사업 수주 기대감에 따른 주가 상승. 미국 원전 건설 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '신사업', '건설']</t>
+          <t>['원전', '건설', '신사업']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+10.70%</t>
+          <t>+9.36%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
         <v>5.34</v>
@@ -1162,7 +1162,7 @@
         <v>5.29</v>
       </c>
       <c r="O8" t="n">
-        <v>6781829232</v>
+        <v>6955160437</v>
       </c>
       <c r="P8" t="n">
         <v>901</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>상장폐지 가능성 속 정리매매 진행, 상속 지분 및 자산 가치 언급.</t>
+          <t>상장폐지 가능성 속 정리매매 시점과 회사 자산 가치에 대한 의견 대립.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['상장폐지', '정리매매', '자산 가치']</t>
+          <t>['상장폐지', '정리매매', '자산가치']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11700</v>
+        <v>11750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.14%</t>
+          <t>+7.60%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.11</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G9" t="n">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="H9" t="n">
         <v>5.42</v>
@@ -1254,7 +1254,7 @@
         <v>5.53</v>
       </c>
       <c r="O9" t="n">
-        <v>95919571905</v>
+        <v>97093519980</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원전 섹터 관련 협정 및 투자 소식, 공매도 상환 압박 및 2조 시총 논란.</t>
+          <t>프랑스와의 원자력 협정 및 대미 투자 관련 소식으로 인한 원전 섹터 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '프랑스 협정']</t>
+          <t>['원전', '원자력 협정', '대미 투자']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50400</v>
+        <v>50500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.00%</t>
+          <t>+5.21%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H10" t="n">
         <v>38.34</v>
@@ -1346,7 +1346,7 @@
         <v>38.24</v>
       </c>
       <c r="O10" t="n">
-        <v>92505033275</v>
+        <v>94481112375</v>
       </c>
       <c r="P10" t="n">
         <v>67300</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>건설주 전반의 상승세와 함께 원전, 재건 등 다양한 테마 기대감 존재. 그러나 단기 급등 후 조정 가능성 및 개인 매도세 관찰.</t>
+          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14100</v>
+        <v>14140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.68%</t>
+          <t>+4.97%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.12</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="H11" t="n">
         <v>1.94</v>
@@ -1438,7 +1438,7 @@
         <v>1.82</v>
       </c>
       <c r="O11" t="n">
-        <v>171748424080</v>
+        <v>173900879895</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Texas 소식과 함께 큰 폭 상승 기대, 공매도 물량 언급 및 매물대 소화 과정.</t>
+          <t>Texas 관련 소식과 투기과열지구 지정 판단일에 따른 변동성 예상.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '공매도', '매물대']</t>
+          <t>['광통신', '투기과열', 'Texas']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9180</v>
+        <v>9210</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.56%</t>
+          <t>+4.90%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F12" t="n">
         <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H12" t="n">
         <v>1.68</v>
@@ -1530,7 +1530,7 @@
         <v>1.72</v>
       </c>
       <c r="O12" t="n">
-        <v>90007819410</v>
+        <v>93687652650</v>
       </c>
       <c r="P12" t="n">
         <v>25050</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>91600</v>
+        <v>15310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+4.21%</t>
+          <t>+4.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="E13" t="n">
-        <v>345</v>
+        <v>42</v>
       </c>
       <c r="F13" t="n">
-        <v>221</v>
+        <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>1669</v>
+        <v>45</v>
       </c>
       <c r="H13" t="n">
-        <v>23.63</v>
+        <v>1.72</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>87900</v>
+        <v>14650</v>
       </c>
       <c r="K13" t="n">
-        <v>91200</v>
+        <v>15100</v>
       </c>
       <c r="L13" t="n">
-        <v>93500</v>
+        <v>16680</v>
       </c>
       <c r="M13" t="n">
-        <v>90200</v>
+        <v>14800</v>
       </c>
       <c r="N13" t="n">
-        <v>23.53</v>
+        <v>1.58</v>
       </c>
       <c r="O13" t="n">
-        <v>280149092250</v>
+        <v>42598164105</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>21400</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>12090</v>
       </c>
       <c r="R13" t="n">
-        <v>-211000</v>
+        <v>35000</v>
       </c>
       <c r="S13" t="n">
-        <v>236000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
+          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '텍사스']</t>
+          <t>['단주 거래', '자전거래', '스카이랩스']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>0155E0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1850000</v>
+        <v>91600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.76%</t>
+          <t>+4.21%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>798</v>
+        <v>351</v>
       </c>
       <c r="F14" t="n">
-        <v>477</v>
+        <v>222</v>
       </c>
       <c r="G14" t="n">
-        <v>2039</v>
+        <v>1694</v>
       </c>
       <c r="H14" t="n">
-        <v>50.63</v>
+        <v>23.63</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1783000</v>
+        <v>87900</v>
       </c>
       <c r="K14" t="n">
-        <v>1799000</v>
+        <v>91200</v>
       </c>
       <c r="L14" t="n">
-        <v>1860000</v>
+        <v>93500</v>
       </c>
       <c r="M14" t="n">
-        <v>1777000</v>
+        <v>90200</v>
       </c>
       <c r="N14" t="n">
-        <v>50.5</v>
+        <v>23.53</v>
       </c>
       <c r="O14" t="n">
-        <v>2606620111500</v>
+        <v>285380489700</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>274000</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>55000</v>
+        <v>-211000</v>
       </c>
       <c r="S14" t="n">
-        <v>71000</v>
+        <v>236000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>낸드 메모리 품귀 현상 및 반도체 시즌2 도래 전망. 기관·외인 재매수세 유입되며 300만 돌파 기대감 고조. 자사주 매수 및 숏 악귀 언급.</t>
+          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['낸드 메모리', '반도체', '자사주 매수']</t>
+          <t>['원전', 'SMR', '텍사스']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1763,27 +1763,27 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33850</v>
+        <v>34100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+4.12%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F15" t="n">
         <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H15" t="n">
-        <v>52.67</v>
+        <v>52.69</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>21.02</v>
       </c>
       <c r="O15" t="n">
-        <v>48111481200</v>
+        <v>50851841650</v>
       </c>
       <c r="P15" t="n">
         <v>69500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 웨스팅하우스 지분 인수 및 원전 사업 관련 호재. PBR 저평가 및 공매도 언급.</t>
+          <t>미국 원전 사업 투자 기대감으로 인한 주가 상승. 공매도 세력과의 공방.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '원전', 'PBR']</t>
+          <t>['원전', '투자', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15050</v>
+        <v>1855000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.73%</t>
+          <t>+4.04%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>797</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>478</v>
       </c>
       <c r="G16" t="n">
-        <v>42</v>
+        <v>2101</v>
       </c>
       <c r="H16" t="n">
-        <v>1.72</v>
+        <v>50.63</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14650</v>
+        <v>1783000</v>
       </c>
       <c r="K16" t="n">
-        <v>15100</v>
+        <v>1799000</v>
       </c>
       <c r="L16" t="n">
-        <v>16680</v>
+        <v>1860000</v>
       </c>
       <c r="M16" t="n">
-        <v>14800</v>
+        <v>1777000</v>
       </c>
       <c r="N16" t="n">
-        <v>1.58</v>
+        <v>50.5</v>
       </c>
       <c r="O16" t="n">
-        <v>42075117990</v>
+        <v>2737120166500</v>
       </c>
       <c r="P16" t="n">
-        <v>21400</v>
+        <v>2987000</v>
       </c>
       <c r="Q16" t="n">
-        <v>12090</v>
+        <v>274000</v>
       </c>
       <c r="R16" t="n">
-        <v>35000</v>
+        <v>55000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>스카이랩스 대비 저평가 언급, 단타 및 자전거래 의혹, 보호예수 물량 주의.</t>
+          <t>낸드 메모리 품귀 현상 및 AI 반도체 시장 성장 기대. 30만 전자 목표.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['단타', '자전거래', '보호예수']</t>
+          <t>['낸드', 'AI 반도체', '품귀']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0155E0</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>276000</v>
+        <v>276750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+2.50%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="F17" t="n">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="G17" t="n">
-        <v>1723</v>
+        <v>1641</v>
       </c>
       <c r="H17" t="n">
         <v>46.79</v>
@@ -1981,7 +1981,7 @@
         <v>272000</v>
       </c>
       <c r="L17" t="n">
-        <v>276000</v>
+        <v>277000</v>
       </c>
       <c r="M17" t="n">
         <v>269000</v>
@@ -1990,7 +1990,7 @@
         <v>46.73</v>
       </c>
       <c r="O17" t="n">
-        <v>1719792942750</v>
+        <v>1865055266750</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>자사주 15조 매수 뉴스가 부각되며 주가 상승 기대감 형성. 그러나 일부 투자자들의 매도 움직임과 정치적 언급도 혼재.</t>
+          <t>자사주 매수 및 배당 확대 발표에 따른 주가 상승 기대. 30만 전자 목표.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['자사주 매수', '반도체']</t>
+          <t>['주주환원', '자사주 매수', '배당']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10200</v>
+        <v>10330</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+1.27%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.23</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H18" t="n">
         <v>0.44</v>
@@ -2082,7 +2082,7 @@
         <v>0.21</v>
       </c>
       <c r="O18" t="n">
-        <v>54619762390</v>
+        <v>55680042645</v>
       </c>
       <c r="P18" t="n">
         <v>20850</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>터빈블레이드 수주 기대감, 원전 및 헷지주 분류 논란, 변동성 속 기대감.</t>
+          <t>터빈블레이드 수주 기대감에도 불구하고 주가 움직임에 대한 답답함.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['터빈블레이드', '수주', '가스터빈']</t>
+          <t>['터빈블레이드', '수주', '강재료']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.91%</t>
+          <t>-3.72%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>28039386470</v>
+        <v>28751256630</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>반도체 섹터 조정과 건설주 상승 흐름 속에서 금호건설은 뚜렷한 호재 없이 부진. 광주공항 재개 등 일부 테마 언급.</t>
+          <t>건설주 강세 속 주가 부진. 대규모 투자 프로젝트 관련 언급 및 반등 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['건설', '광주공항']</t>
+          <t>['건설', '투자', '반등']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12160</v>
+        <v>12110</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.10%</t>
+          <t>-4.50%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H20" t="n">
         <v>17.11</v>
@@ -2266,7 +2266,7 @@
         <v>18.05</v>
       </c>
       <c r="O20" t="n">
-        <v>21988104080</v>
+        <v>22719290910</v>
       </c>
       <c r="P20" t="n">
         <v>14350</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>계단식 하락 추세 지속되며 하한가 우려 제기. 반도체 섹터 조정과 외인 프로그램 매도세 속 투자 심리 위축.</t>
+          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['하락 추세', '반도체']</t>
+          <t>['하락', '하한가', '공포']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8430</v>
+        <v>8440</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-10.89%</t>
+          <t>-10.78%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H21" t="n">
         <v>38.84</v>
@@ -2358,7 +2358,7 @@
         <v>38.69</v>
       </c>
       <c r="O21" t="n">
-        <v>22510046425</v>
+        <v>23113652335</v>
       </c>
       <c r="P21" t="n">
         <v>19150</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>삼성, 포스코 관계사 대비 부진, 매도 조장 및 대차잔고 관련 우려.</t>
+          <t>삼성, 포스코 관련주 상승 대비 부진한 주가 흐름과 조정에 대한 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['포스코', '대차잔고', '매도 조장']</t>
+          <t>['포스코', '삼성', '조정']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2418,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G22" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H22" t="n">
         <v>0.08</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>감사의견 적정으로 거래 재개 기대감 있었으나, 유증 물량과 재무 상태에 대한 우려로 주가 급락. 향후 전망 불투명.</t>
+          <t>감사의견 적정 판정 후 주가 급락. 재무 건전성 우려 및 상폐 가능성 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['감사의견', '유증']</t>
+          <t>['감사의견', '재무', '상장폐지']</t>
         </is>
       </c>
       <c r="X22" t="n">
